--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:45</t>
+    <t xml:space="preserve">2026-09-09 23:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:45</t>
+    <t xml:space="preserve">2026-09-18 10:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:33</t>
+    <t xml:space="preserve">2026-09-23 13:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:05</t>
+    <t xml:space="preserve">2026-10-02 15:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Tomé</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Concepción</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:21</t>
+    <t xml:space="preserve">2026-10-04 09:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:51</t>
+    <t xml:space="preserve">2026-10-05 13:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
